--- a/experiments/20250529_rough/iteration_1/raw_data/raw_absorbance_i1.xlsx
+++ b/experiments/20250529_rough/iteration_1/raw_data/raw_absorbance_i1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Surfactant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4747A61-6C77-49E1-A583-62EA726E3897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{509460DF-CA19-4E4C-B78E-14D9A7ED0E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1812" yWindow="1812" windowWidth="9648" windowHeight="10596"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="Plate 1 - Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MethodPointer1">-532077696</definedName>
-    <definedName name="MethodPointer2">573</definedName>
+    <definedName name="MethodPointer1">314425904</definedName>
+    <definedName name="MethodPointer2">637</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Software Version</t>
   </si>
@@ -46,7 +46,7 @@
     <t>Experiment File Path:</t>
   </si>
   <si>
-    <t>D:\Surfactant\Plate-1-SDS-IBP -OD600.xpt</t>
+    <t>D:\Surfactant\otflex_1.xpt</t>
   </si>
   <si>
     <t>Protocol File Path:</t>
@@ -73,9 +73,6 @@
     <t>Reader Serial Number:</t>
   </si>
   <si>
-    <t>Unknown</t>
-  </si>
-  <si>
     <t>Reading Type</t>
   </si>
   <si>
@@ -100,7 +97,7 @@
     <t>Absorbance Endpoint</t>
   </si>
   <si>
-    <t>A1..D12</t>
+    <t>G1..G12</t>
   </si>
   <si>
     <t>Wavelengths:  600</t>
@@ -190,7 +187,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F3FF"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8E9F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E0F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -202,37 +211,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9CC5E5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF428EC7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5197CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF247CBD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3385C2"/>
+        <fgColor rgb="FFBAD7EF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF8DBCE0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F3FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -283,6 +280,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -297,9 +297,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -682,7 +679,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>45806</v>
+        <v>45807</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -690,7 +687,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>0.3964699074074074</v>
+        <v>0.63150462962962961</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -705,72 +702,72 @@
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="s">
-        <v>12</v>
+      <c r="B10">
+        <v>24011019</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
         <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" s="4"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
         <v>16</v>
-      </c>
-      <c r="B14" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
         <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" s="4"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22">
-        <v>25.5</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -814,257 +811,185 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="7">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="D25" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="E25" s="7">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="F25" s="8">
-        <v>0.501</v>
-      </c>
-      <c r="G25" s="9">
-        <v>0.57499999999999996</v>
-      </c>
-      <c r="H25" s="9">
-        <v>0.51</v>
-      </c>
-      <c r="I25" s="10">
-        <v>1.087</v>
-      </c>
-      <c r="J25" s="11">
-        <v>1.0580000000000001</v>
-      </c>
-      <c r="K25" s="12">
-        <v>1.3360000000000001</v>
-      </c>
-      <c r="L25" s="7">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="M25" s="7">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="N25" s="7">
-        <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="O25" s="13">
+        <v>25</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="8">
         <v>600</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="12">
-        <v>1.2809999999999999</v>
-      </c>
-      <c r="D26" s="12">
-        <v>1.27</v>
-      </c>
-      <c r="E26" s="14">
-        <v>1.2250000000000001</v>
-      </c>
-      <c r="F26" s="7">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="G26" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="H26" s="7">
-        <v>3.7999999999999999E-2</v>
-      </c>
-      <c r="I26" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="J26" s="7">
-        <v>3.9E-2</v>
-      </c>
-      <c r="K26" s="7">
-        <v>3.9E-2</v>
-      </c>
-      <c r="L26" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="M26" s="7">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="N26" s="7">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="O26" s="13">
+        <v>26</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="8">
         <v>600</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="D27" s="7">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="E27" s="7">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="F27" s="7">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="G27" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="H27" s="7">
-        <v>3.9E-2</v>
-      </c>
-      <c r="I27" s="7">
-        <v>3.9E-2</v>
-      </c>
-      <c r="J27" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="K27" s="7">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="L27" s="7">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="M27" s="7">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="N27" s="7">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="O27" s="13">
+        <v>27</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="8">
         <v>600</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="7">
-        <v>3.9E-2</v>
-      </c>
-      <c r="D28" s="7">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="F28" s="7">
-        <v>3.9E-2</v>
-      </c>
-      <c r="G28" s="7">
-        <v>3.9E-2</v>
-      </c>
-      <c r="H28" s="7">
-        <v>3.9E-2</v>
-      </c>
-      <c r="I28" s="7">
-        <v>4.7E-2</v>
-      </c>
-      <c r="J28" s="7">
-        <v>4.5999999999999999E-2</v>
-      </c>
-      <c r="K28" s="7">
-        <v>4.7E-2</v>
-      </c>
-      <c r="L28" s="7">
-        <v>4.8000000000000001E-2</v>
-      </c>
-      <c r="M28" s="7">
-        <v>4.7E-2</v>
-      </c>
-      <c r="N28" s="7">
-        <v>4.8000000000000001E-2</v>
-      </c>
-      <c r="O28" s="13">
+        <v>28</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+      <c r="O28" s="8">
         <v>600</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="15"/>
-      <c r="O29" s="13">
+        <v>29</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="8">
         <v>600</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15"/>
-      <c r="O30" s="13">
+        <v>30</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+      <c r="O30" s="8">
         <v>600</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="13">
+        <v>31</v>
+      </c>
+      <c r="C31" s="9">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="D31" s="10">
+        <v>3.9E-2</v>
+      </c>
+      <c r="E31" s="10">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="F31" s="11">
+        <v>0.04</v>
+      </c>
+      <c r="G31" s="12">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="H31" s="13">
+        <v>3.9E-2</v>
+      </c>
+      <c r="I31" s="13">
+        <v>3.9E-2</v>
+      </c>
+      <c r="J31" s="14">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="K31" s="11">
+        <v>0.04</v>
+      </c>
+      <c r="L31" s="9">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="M31" s="15">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="N31" s="15">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="O31" s="8">
         <v>600</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="15"/>
-      <c r="O32" s="13">
+        <v>32</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
+      <c r="O32" s="8">
         <v>600</v>
       </c>
     </row>
